--- a/examples/branch_reports/深圳分公司_统计.xlsx
+++ b/examples/branch_reports/深圳分公司_统计.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\合并花名册.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
